--- a/docs/03_test/部署削除画面テスト.xlsx
+++ b/docs/03_test/部署削除画面テスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D261789D-9750-439B-B20C-34284119C537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FF68D7-7ED5-4EBA-A88D-EF7112FBD81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3E5A4180-5218-4287-B943-DC5463A34754}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3E5A4180-5218-4287-B943-DC5463A34754}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -163,16 +163,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部署一覧テスト</t>
-    <rPh sb="0" eb="2">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストの対象と範囲</t>
     <rPh sb="4" eb="6">
       <t>タイショウ</t>
@@ -264,6 +254,16 @@
   </si>
   <si>
     <t>No.2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署削除テスト</t>
+    <rPh sb="0" eb="2">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -390,44 +390,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,119 +1155,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="8"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="10"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="6"/>
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="12"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="13"/>
-      <c r="C7" s="9" t="s">
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C20" s="9" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="5">
-        <v>1</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="5">
-        <v>2</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="13"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="6"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
@@ -1277,7 +1278,6 @@
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/03_test/部署削除画面テスト.xlsx
+++ b/docs/03_test/部署削除画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FF68D7-7ED5-4EBA-A88D-EF7112FBD81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05375F66-74DC-4003-97F2-8A5689CB2231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3E5A4180-5218-4287-B943-DC5463A34754}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="部署削除テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -408,12 +408,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -424,9 +427,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1155,34 +1155,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="7"/>
     </row>
     <row r="4" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="6"/>
@@ -1196,30 +1196,30 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="12"/>
+      <c r="B34" s="13"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1">
@@ -1250,10 +1250,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="7"/>
+      <c r="B40" s="9"/>
       <c r="C40" s="6"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
